--- a/legasus/backend/data/customers.xlsx
+++ b/legasus/backend/data/customers.xlsx
@@ -448,7 +448,7 @@
         <v>Legasus</v>
       </c>
       <c r="D2" t="str">
-        <v>admin@legasus.com</v>
+        <v>legasus.co@gmail.com</v>
       </c>
       <c r="E2" t="str">
         <v>6b62404f9ce4c1c420bad34a46eb0c9011422361b929a4f44a11f4117ab985e63857950602e2063663aed3e2b1fb63c53d828ff9040e7150ae0dcade3e0fc248</v>
